--- a/artfynd/A 36783-2023 artfynd.xlsx
+++ b/artfynd/A 36783-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126402813</v>
       </c>
       <c r="B2" t="n">
-        <v>55440</v>
+        <v>55441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 36783-2023 artfynd.xlsx
+++ b/artfynd/A 36783-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126402813</v>
+        <v>126402812</v>
       </c>
       <c r="B2" t="n">
-        <v>55441</v>
+        <v>56338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206063</v>
+        <v>100127</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ål</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguilla anguilla</t>
+          <t>Salmo trutta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -774,6 +774,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126402813</v>
+      </c>
+      <c r="B3" t="n">
+        <v>55724</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>206063</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anguilla anguilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lillån, Grustäkt, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>344952</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6368356</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Surteby-Kattunga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1993-08-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1993-08-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Elfiske fr Lst, gammal artuppgift, inlagd av Marks Kommun</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
